--- a/artfynd/A 933-2026 artfynd.xlsx
+++ b/artfynd/A 933-2026 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>130826010</v>
+        <v>130825823</v>
       </c>
       <c r="B2" t="n">
-        <v>91775</v>
+        <v>57861</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,34 +686,39 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Flinktorpet, Flinktorpet, Jmt</t>
+          <t>Flinktorpet, Kälom, Offerdal, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>460971</v>
+        <v>460947</v>
       </c>
       <c r="R2" t="n">
-        <v>7039688</v>
+        <v>7039711</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,7 +760,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>10:38</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Födosökshål på äldre döende gran.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,10 +792,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130825823</v>
+        <v>130826784</v>
       </c>
       <c r="B3" t="n">
-        <v>57860</v>
+        <v>57864</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,16 +803,16 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -813,19 +823,19 @@
       <c r="I3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Flinktorpet, Kälom, Offerdal, Jmt</t>
+          <t>Brännan, Kälom, Offerdal, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>460947</v>
+        <v>461233</v>
       </c>
       <c r="R3" t="n">
-        <v>7039711</v>
+        <v>7039438</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -857,7 +867,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -867,12 +877,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Födosökshål på äldre döende gran.</t>
+          <t>Födosök barkfläk</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,10 +909,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130826784</v>
+        <v>130825852</v>
       </c>
       <c r="B4" t="n">
-        <v>57863</v>
+        <v>57864</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -935,17 +945,17 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Brännan, Kälom, Offerdal, Jmt</t>
+          <t>Flinktorpet, Kälom, Offerdal, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>461233</v>
+        <v>460952</v>
       </c>
       <c r="R4" t="n">
-        <v>7039438</v>
+        <v>7039723</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -974,7 +984,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -984,12 +994,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Födosök barkfläk</t>
+          <t>Barkfläkta grövre och klenare granar.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1016,10 +1026,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130825852</v>
+        <v>130826010</v>
       </c>
       <c r="B5" t="n">
-        <v>57863</v>
+        <v>91776</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1027,42 +1037,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Flinktorpet, Kälom, Offerdal, Jmt</t>
+          <t>Flinktorpet, Flinktorpet, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>460952</v>
+        <v>460971</v>
       </c>
       <c r="R5" t="n">
-        <v>7039723</v>
+        <v>7039688</v>
       </c>
       <c r="S5" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1091,7 +1096,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1101,12 +1106,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:42</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Barkfläkta grövre och klenare granar.</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1136,7 +1136,7 @@
         <v>130826011</v>
       </c>
       <c r="B6" t="n">
-        <v>92234</v>
+        <v>92235</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1248,7 +1248,7 @@
         <v>130826404</v>
       </c>
       <c r="B7" t="n">
-        <v>57863</v>
+        <v>57864</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1365,7 +1365,7 @@
         <v>130825491</v>
       </c>
       <c r="B8" t="n">
-        <v>79220</v>
+        <v>79221</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1486,7 +1486,7 @@
         <v>130826097</v>
       </c>
       <c r="B9" t="n">
-        <v>57863</v>
+        <v>57864</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1720,7 +1720,7 @@
         <v>130825838</v>
       </c>
       <c r="B11" t="n">
-        <v>79220</v>
+        <v>79221</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1829,10 +1829,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130826137</v>
+        <v>130826478</v>
       </c>
       <c r="B12" t="n">
-        <v>91775</v>
+        <v>57864</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1840,34 +1840,39 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Flinktorpet, Flinktorpet, Jmt</t>
+          <t>Brännan, Kälom, Offerdal, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>461026</v>
+        <v>461220</v>
       </c>
       <c r="R12" t="n">
-        <v>7039757</v>
+        <v>7039590</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1899,7 +1904,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1909,7 +1914,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>11:25</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Födosök barkfläkt</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1939,7 +1949,7 @@
         <v>130826287</v>
       </c>
       <c r="B13" t="n">
-        <v>57863</v>
+        <v>57864</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2053,10 +2063,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130826478</v>
+        <v>130826137</v>
       </c>
       <c r="B14" t="n">
-        <v>57863</v>
+        <v>91776</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2064,39 +2074,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Brännan, Kälom, Offerdal, Jmt</t>
+          <t>Flinktorpet, Flinktorpet, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>461220</v>
+        <v>461026</v>
       </c>
       <c r="R14" t="n">
-        <v>7039590</v>
+        <v>7039757</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2128,7 +2133,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2138,12 +2143,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>11:25</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Födosök barkfläkt</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2173,7 +2173,7 @@
         <v>130826795</v>
       </c>
       <c r="B15" t="n">
-        <v>91775</v>
+        <v>91776</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2280,7 +2280,7 @@
         <v>130826291</v>
       </c>
       <c r="B16" t="n">
-        <v>91775</v>
+        <v>91776</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2387,7 +2387,7 @@
         <v>130825822</v>
       </c>
       <c r="B17" t="n">
-        <v>89168</v>
+        <v>89169</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2499,7 +2499,7 @@
         <v>130826442</v>
       </c>
       <c r="B18" t="n">
-        <v>91775</v>
+        <v>91776</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2606,7 +2606,7 @@
         <v>130826276</v>
       </c>
       <c r="B19" t="n">
-        <v>79220</v>
+        <v>79221</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2715,10 +2715,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>130826274</v>
+        <v>130825533</v>
       </c>
       <c r="B20" t="n">
-        <v>57863</v>
+        <v>57864</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2746,19 +2746,19 @@
       <c r="I20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Flinktorpet, Kälom, Offerdal, Jmt</t>
+          <t>Flinktorpet, Flinktorpet, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>461045</v>
+        <v>460944</v>
       </c>
       <c r="R20" t="n">
-        <v>7039737</v>
+        <v>7039740</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2790,7 +2790,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>10:26</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2800,12 +2800,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>10:26</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Färska spår födosök, barkfläkta klenare granar.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2832,10 +2832,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>130825533</v>
+        <v>130826274</v>
       </c>
       <c r="B21" t="n">
-        <v>57863</v>
+        <v>57864</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2863,19 +2863,19 @@
       <c r="I21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Flinktorpet, Flinktorpet, Jmt</t>
+          <t>Flinktorpet, Kälom, Offerdal, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>460944</v>
+        <v>461045</v>
       </c>
       <c r="R21" t="n">
-        <v>7039740</v>
+        <v>7039737</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2907,7 +2907,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>10:26</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2917,12 +2917,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>10:26</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Färska spår födosök, barkfläkta klenare granar.</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2952,7 +2952,7 @@
         <v>130826355</v>
       </c>
       <c r="B22" t="n">
-        <v>92502</v>
+        <v>92503</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3064,7 +3064,7 @@
         <v>130826438</v>
       </c>
       <c r="B23" t="n">
-        <v>79220</v>
+        <v>79221</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 933-2026 artfynd.xlsx
+++ b/artfynd/A 933-2026 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>130825823</v>
+        <v>130826010</v>
       </c>
       <c r="B2" t="n">
-        <v>57861</v>
+        <v>91776</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,39 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Flinktorpet, Kälom, Offerdal, Jmt</t>
+          <t>Flinktorpet, Flinktorpet, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>460947</v>
+        <v>460971</v>
       </c>
       <c r="R2" t="n">
-        <v>7039711</v>
+        <v>7039688</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,12 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>10:38</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Födosökshål på äldre döende gran.</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -1026,10 +1016,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130826010</v>
+        <v>130825823</v>
       </c>
       <c r="B5" t="n">
-        <v>91776</v>
+        <v>57861</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1037,34 +1027,39 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Flinktorpet, Flinktorpet, Jmt</t>
+          <t>Flinktorpet, Kälom, Offerdal, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>460971</v>
+        <v>460947</v>
       </c>
       <c r="R5" t="n">
-        <v>7039688</v>
+        <v>7039711</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1096,7 +1091,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1106,7 +1101,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>10:38</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Födosökshål på äldre döende gran.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1829,7 +1829,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130826478</v>
+        <v>130826287</v>
       </c>
       <c r="B12" t="n">
         <v>57864</v>
@@ -1865,14 +1865,14 @@
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Brännan, Kälom, Offerdal, Jmt</t>
+          <t>Flinktorpet, Kälom, Offerdal, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>461220</v>
+        <v>461096</v>
       </c>
       <c r="R12" t="n">
-        <v>7039590</v>
+        <v>7039690</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1904,7 +1904,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1914,12 +1914,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Födosök barkfläkt</t>
+          <t>Barkfläkta klenare och grövre granar</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1946,7 +1946,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130826287</v>
+        <v>130826478</v>
       </c>
       <c r="B13" t="n">
         <v>57864</v>
@@ -1982,14 +1982,14 @@
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Flinktorpet, Kälom, Offerdal, Jmt</t>
+          <t>Brännan, Kälom, Offerdal, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>461096</v>
+        <v>461220</v>
       </c>
       <c r="R13" t="n">
-        <v>7039690</v>
+        <v>7039590</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2021,7 +2021,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2031,12 +2031,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Barkfläkta klenare och grövre granar</t>
+          <t>Födosök barkfläkt</t>
         </is>
       </c>
       <c r="AD13" t="b">

--- a/artfynd/A 933-2026 artfynd.xlsx
+++ b/artfynd/A 933-2026 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>130826010</v>
+        <v>130826784</v>
       </c>
       <c r="B2" t="n">
-        <v>91776</v>
+        <v>57864</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,34 +686,39 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Flinktorpet, Flinktorpet, Jmt</t>
+          <t>Brännan, Kälom, Offerdal, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>460971</v>
+        <v>461233</v>
       </c>
       <c r="R2" t="n">
-        <v>7039688</v>
+        <v>7039438</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,7 +760,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>11:37</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Födosök barkfläk</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,10 +792,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130826784</v>
+        <v>130825823</v>
       </c>
       <c r="B3" t="n">
-        <v>57864</v>
+        <v>57861</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -793,16 +803,16 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -813,19 +823,19 @@
       <c r="I3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Brännan, Kälom, Offerdal, Jmt</t>
+          <t>Flinktorpet, Kälom, Offerdal, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>461233</v>
+        <v>460947</v>
       </c>
       <c r="R3" t="n">
-        <v>7039438</v>
+        <v>7039711</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -857,7 +867,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -867,12 +877,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Födosök barkfläk</t>
+          <t>Födosökshål på äldre döende gran.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -1016,10 +1026,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130825823</v>
+        <v>130826010</v>
       </c>
       <c r="B5" t="n">
-        <v>57861</v>
+        <v>91776</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1027,39 +1037,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Flinktorpet, Kälom, Offerdal, Jmt</t>
+          <t>Flinktorpet, Flinktorpet, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>460947</v>
+        <v>460971</v>
       </c>
       <c r="R5" t="n">
-        <v>7039711</v>
+        <v>7039688</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1091,7 +1096,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1101,12 +1106,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:38</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Födosökshål på äldre döende gran.</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1829,7 +1829,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130826287</v>
+        <v>130826478</v>
       </c>
       <c r="B12" t="n">
         <v>57864</v>
@@ -1865,14 +1865,14 @@
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Flinktorpet, Kälom, Offerdal, Jmt</t>
+          <t>Brännan, Kälom, Offerdal, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>461096</v>
+        <v>461220</v>
       </c>
       <c r="R12" t="n">
-        <v>7039690</v>
+        <v>7039590</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1904,7 +1904,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1914,12 +1914,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Barkfläkta klenare och grövre granar</t>
+          <t>Födosök barkfläkt</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1946,10 +1946,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130826478</v>
+        <v>130826137</v>
       </c>
       <c r="B13" t="n">
-        <v>57864</v>
+        <v>91776</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1957,39 +1957,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Brännan, Kälom, Offerdal, Jmt</t>
+          <t>Flinktorpet, Flinktorpet, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>461220</v>
+        <v>461026</v>
       </c>
       <c r="R13" t="n">
-        <v>7039590</v>
+        <v>7039757</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2021,7 +2016,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2031,12 +2026,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>11:25</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Födosök barkfläkt</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2063,10 +2053,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130826137</v>
+        <v>130826287</v>
       </c>
       <c r="B14" t="n">
-        <v>91776</v>
+        <v>57864</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2074,34 +2064,39 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Flinktorpet, Flinktorpet, Jmt</t>
+          <t>Flinktorpet, Kälom, Offerdal, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>461026</v>
+        <v>461096</v>
       </c>
       <c r="R14" t="n">
-        <v>7039757</v>
+        <v>7039690</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2133,7 +2128,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2143,7 +2138,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>11:04</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Barkfläkta klenare och grövre granar</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2949,48 +2949,48 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>130826355</v>
+        <v>130826438</v>
       </c>
       <c r="B22" t="n">
-        <v>92503</v>
+        <v>79221</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>67</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Sprickporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Diplomitoporus crustulinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Bres.) Domański</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Flinktorpet, Flinktorpet, Jmt</t>
+          <t>Brännan, Brännan, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>461117</v>
+        <v>461220</v>
       </c>
       <c r="R22" t="n">
-        <v>7039629</v>
+        <v>7039590</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3019,7 +3019,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3029,12 +3029,12 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>På undersidan av lutande död gran.</t>
+          <t>Rikligt i området</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3061,48 +3061,48 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>130826438</v>
+        <v>130826355</v>
       </c>
       <c r="B23" t="n">
-        <v>79221</v>
+        <v>92503</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>67</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Sprickporing</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Diplomitoporus crustulinus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Bres.) Domański</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Brännan, Brännan, Jmt</t>
+          <t>Flinktorpet, Flinktorpet, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>461220</v>
+        <v>461117</v>
       </c>
       <c r="R23" t="n">
-        <v>7039590</v>
+        <v>7039629</v>
       </c>
       <c r="S23" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3131,7 +3131,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3141,12 +3141,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Rikligt i området</t>
+          <t>På undersidan av lutande död gran.</t>
         </is>
       </c>
       <c r="AD23" t="b">

--- a/artfynd/A 933-2026 artfynd.xlsx
+++ b/artfynd/A 933-2026 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>130826784</v>
+        <v>130825852</v>
       </c>
       <c r="B2" t="n">
         <v>57864</v>
@@ -711,17 +711,17 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Brännan, Kälom, Offerdal, Jmt</t>
+          <t>Flinktorpet, Kälom, Offerdal, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>461233</v>
+        <v>460952</v>
       </c>
       <c r="R2" t="n">
-        <v>7039438</v>
+        <v>7039723</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,12 +760,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Födosök barkfläk</t>
+          <t>Barkfläkta grövre och klenare granar.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -792,10 +792,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130825823</v>
+        <v>130826784</v>
       </c>
       <c r="B3" t="n">
-        <v>57861</v>
+        <v>57864</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -803,16 +803,16 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -823,19 +823,19 @@
       <c r="I3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Flinktorpet, Kälom, Offerdal, Jmt</t>
+          <t>Brännan, Kälom, Offerdal, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>460947</v>
+        <v>461233</v>
       </c>
       <c r="R3" t="n">
-        <v>7039711</v>
+        <v>7039438</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -867,7 +867,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -877,12 +877,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Födosökshål på äldre döende gran.</t>
+          <t>Födosök barkfläk</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -909,10 +909,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130825852</v>
+        <v>130825823</v>
       </c>
       <c r="B4" t="n">
-        <v>57864</v>
+        <v>57861</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -920,16 +920,16 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -940,7 +940,7 @@
       <c r="I4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -949,13 +949,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>460952</v>
+        <v>460947</v>
       </c>
       <c r="R4" t="n">
-        <v>7039723</v>
+        <v>7039711</v>
       </c>
       <c r="S4" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -984,7 +984,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Barkfläkta grövre och klenare granar.</t>
+          <t>Födosökshål på äldre döende gran.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1829,7 +1829,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130826478</v>
+        <v>130826287</v>
       </c>
       <c r="B12" t="n">
         <v>57864</v>
@@ -1865,14 +1865,14 @@
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Brännan, Kälom, Offerdal, Jmt</t>
+          <t>Flinktorpet, Kälom, Offerdal, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>461220</v>
+        <v>461096</v>
       </c>
       <c r="R12" t="n">
-        <v>7039590</v>
+        <v>7039690</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1904,7 +1904,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1914,12 +1914,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Födosök barkfläkt</t>
+          <t>Barkfläkta klenare och grövre granar</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1946,10 +1946,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130826137</v>
+        <v>130826478</v>
       </c>
       <c r="B13" t="n">
-        <v>91776</v>
+        <v>57864</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1957,34 +1957,39 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Flinktorpet, Flinktorpet, Jmt</t>
+          <t>Brännan, Kälom, Offerdal, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>461026</v>
+        <v>461220</v>
       </c>
       <c r="R13" t="n">
-        <v>7039757</v>
+        <v>7039590</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2016,7 +2021,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2026,7 +2031,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>11:25</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Födosök barkfläkt</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2053,10 +2063,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130826287</v>
+        <v>130826137</v>
       </c>
       <c r="B14" t="n">
-        <v>57864</v>
+        <v>91776</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2064,39 +2074,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Flinktorpet, Kälom, Offerdal, Jmt</t>
+          <t>Flinktorpet, Flinktorpet, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>461096</v>
+        <v>461026</v>
       </c>
       <c r="R14" t="n">
-        <v>7039690</v>
+        <v>7039757</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2128,7 +2133,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2138,12 +2143,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>11:04</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Barkfläkta klenare och grövre granar</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AD14" t="b">

--- a/artfynd/A 933-2026 artfynd.xlsx
+++ b/artfynd/A 933-2026 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>130825852</v>
+        <v>130825823</v>
       </c>
       <c r="B2" t="n">
-        <v>57864</v>
+        <v>57861</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,16 +686,16 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -706,7 +706,7 @@
       <c r="I2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -715,13 +715,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>460952</v>
+        <v>460947</v>
       </c>
       <c r="R2" t="n">
-        <v>7039723</v>
+        <v>7039711</v>
       </c>
       <c r="S2" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,12 +760,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Barkfläkta grövre och klenare granar.</t>
+          <t>Födosökshål på äldre döende gran.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -792,10 +792,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130826784</v>
+        <v>130826010</v>
       </c>
       <c r="B3" t="n">
-        <v>57864</v>
+        <v>91776</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -803,39 +803,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Brännan, Kälom, Offerdal, Jmt</t>
+          <t>Flinktorpet, Flinktorpet, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>461233</v>
+        <v>460971</v>
       </c>
       <c r="R3" t="n">
-        <v>7039438</v>
+        <v>7039688</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -867,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -877,12 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:37</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Födosök barkfläk</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -909,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130825823</v>
+        <v>130826784</v>
       </c>
       <c r="B4" t="n">
-        <v>57861</v>
+        <v>57864</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -920,16 +910,16 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -940,19 +930,19 @@
       <c r="I4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Flinktorpet, Kälom, Offerdal, Jmt</t>
+          <t>Brännan, Kälom, Offerdal, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>460947</v>
+        <v>461233</v>
       </c>
       <c r="R4" t="n">
-        <v>7039711</v>
+        <v>7039438</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -984,7 +974,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -994,12 +984,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Födosökshål på äldre döende gran.</t>
+          <t>Födosök barkfläk</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1026,10 +1016,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130826010</v>
+        <v>130825852</v>
       </c>
       <c r="B5" t="n">
-        <v>91776</v>
+        <v>57864</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1037,37 +1027,42 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Flinktorpet, Flinktorpet, Jmt</t>
+          <t>Flinktorpet, Kälom, Offerdal, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>460971</v>
+        <v>460952</v>
       </c>
       <c r="R5" t="n">
-        <v>7039688</v>
+        <v>7039723</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1096,7 +1091,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1106,7 +1101,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>10:42</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Barkfläkta grövre och klenare granar.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1829,10 +1829,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130826287</v>
+        <v>130826137</v>
       </c>
       <c r="B12" t="n">
-        <v>57864</v>
+        <v>91776</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1840,39 +1840,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Flinktorpet, Kälom, Offerdal, Jmt</t>
+          <t>Flinktorpet, Flinktorpet, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>461096</v>
+        <v>461026</v>
       </c>
       <c r="R12" t="n">
-        <v>7039690</v>
+        <v>7039757</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1904,7 +1899,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1914,12 +1909,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>11:04</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Barkfläkta klenare och grövre granar</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1946,7 +1936,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130826478</v>
+        <v>130826287</v>
       </c>
       <c r="B13" t="n">
         <v>57864</v>
@@ -1982,14 +1972,14 @@
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Brännan, Kälom, Offerdal, Jmt</t>
+          <t>Flinktorpet, Kälom, Offerdal, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>461220</v>
+        <v>461096</v>
       </c>
       <c r="R13" t="n">
-        <v>7039590</v>
+        <v>7039690</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2021,7 +2011,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2031,12 +2021,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Födosök barkfläkt</t>
+          <t>Barkfläkta klenare och grövre granar</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2063,10 +2053,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130826137</v>
+        <v>130826478</v>
       </c>
       <c r="B14" t="n">
-        <v>91776</v>
+        <v>57864</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2074,34 +2064,39 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Flinktorpet, Flinktorpet, Jmt</t>
+          <t>Brännan, Kälom, Offerdal, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>461026</v>
+        <v>461220</v>
       </c>
       <c r="R14" t="n">
-        <v>7039757</v>
+        <v>7039590</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2133,7 +2128,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2143,7 +2138,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>11:25</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Födosök barkfläkt</t>
         </is>
       </c>
       <c r="AD14" t="b">

--- a/artfynd/A 933-2026 artfynd.xlsx
+++ b/artfynd/A 933-2026 artfynd.xlsx
@@ -675,50 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>130825823</v>
+        <v>130826355</v>
       </c>
       <c r="B2" t="n">
-        <v>57881</v>
+        <v>92637</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>67</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Sprickporing</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Diplomitoporus crustulinus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Bres.) Domański</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Flinktorpet, Kälom, Offerdal, Jmt</t>
+          <t>Flinktorpet, Flinktorpet, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>460947</v>
+        <v>461117</v>
       </c>
       <c r="R2" t="n">
-        <v>7039711</v>
+        <v>7039629</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,12 +755,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>11:10</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Födosökshål på äldre döende gran.</t>
+          <t>På undersidan av lutande död gran.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -792,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130826784</v>
+        <v>130825822</v>
       </c>
       <c r="B3" t="n">
-        <v>57884</v>
+        <v>89292</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -803,39 +798,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>510</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Brännan, Kälom, Offerdal, Jmt</t>
+          <t>Flinktorpet, Flinktorpet, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>461233</v>
+        <v>460947</v>
       </c>
       <c r="R3" t="n">
-        <v>7039438</v>
+        <v>7039711</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -867,7 +857,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -877,12 +867,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Födosök barkfläk</t>
+          <t>På granlåga</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -909,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>130825852</v>
+        <v>130826010</v>
       </c>
       <c r="B4" t="n">
-        <v>57884</v>
+        <v>91909</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -920,42 +910,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Flinktorpet, Kälom, Offerdal, Jmt</t>
+          <t>Flinktorpet, Flinktorpet, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>460952</v>
+        <v>460971</v>
       </c>
       <c r="R4" t="n">
-        <v>7039723</v>
+        <v>7039688</v>
       </c>
       <c r="S4" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -984,7 +969,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -994,12 +979,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:42</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Barkfläkta grövre och klenare granar.</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1026,10 +1006,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130826010</v>
+        <v>130826137</v>
       </c>
       <c r="B5" t="n">
-        <v>91809</v>
+        <v>91909</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1061,10 +1041,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>460971</v>
+        <v>461026</v>
       </c>
       <c r="R5" t="n">
-        <v>7039688</v>
+        <v>7039757</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1096,7 +1076,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1106,7 +1086,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>10:56</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1133,32 +1113,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130826011</v>
+        <v>130826291</v>
       </c>
       <c r="B6" t="n">
-        <v>92268</v>
+        <v>91909</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1168,10 +1148,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>460969</v>
+        <v>461106</v>
       </c>
       <c r="R6" t="n">
-        <v>7039684</v>
+        <v>7039672</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1203,7 +1183,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:48</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1213,12 +1193,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:48</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>På granlåga med ullticka</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1245,10 +1220,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130826404</v>
+        <v>130826442</v>
       </c>
       <c r="B7" t="n">
-        <v>57884</v>
+        <v>91909</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1256,39 +1231,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Brännan, Brännan, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>461144</v>
+        <v>461220</v>
       </c>
       <c r="R7" t="n">
-        <v>7039619</v>
+        <v>7039590</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1320,7 +1290,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1330,12 +1300,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:14</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Födosök barkfläkt</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1362,10 +1327,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>130825491</v>
+        <v>130826795</v>
       </c>
       <c r="B8" t="n">
-        <v>79244</v>
+        <v>91909</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1373,43 +1338,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1000</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Flinktorpet, Flinktorpet, Jmt</t>
+          <t>Brännan, Brännan, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>460932</v>
+        <v>461233</v>
       </c>
       <c r="R8" t="n">
-        <v>7039739</v>
+        <v>7039441</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1441,7 +1397,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10:26</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1451,12 +1407,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>10:26</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Rikligt med bålar på äldre gran i området.</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1483,10 +1434,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>130826097</v>
+        <v>130826011</v>
       </c>
       <c r="B9" t="n">
-        <v>57884</v>
+        <v>92369</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1494,32 +1445,27 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>1209</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Flinktorpet, Kälom, Offerdal, Jmt</t>
+          <t>Flinktorpet, Flinktorpet, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
@@ -1558,7 +1504,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1568,12 +1514,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>10:48</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Färska och äldre ringhack</t>
+          <t>På granlåga med ullticka</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1600,50 +1546,54 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130826548</v>
+        <v>130825491</v>
       </c>
       <c r="B10" t="n">
-        <v>56699</v>
+        <v>79327</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100077</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Utter</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lutra lutra</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Brännan, Brännan, Jmt</t>
+          <t>Flinktorpet, Flinktorpet, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>461350</v>
+        <v>460932</v>
       </c>
       <c r="R10" t="n">
-        <v>7039491</v>
+        <v>7039739</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1675,7 +1625,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>10:26</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1685,12 +1635,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>10:26</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Kommit från väster och gått längs bäcken.</t>
+          <t>Rikligt med bålar på äldre gran i området.</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1720,11 +1670,11 @@
         <v>130825838</v>
       </c>
       <c r="B11" t="n">
-        <v>79244</v>
+        <v>79327</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
@@ -1829,32 +1779,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>130826137</v>
+        <v>130826276</v>
       </c>
       <c r="B12" t="n">
-        <v>91809</v>
+        <v>79327</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1864,13 +1814,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>461026</v>
+        <v>461045</v>
       </c>
       <c r="R12" t="n">
-        <v>7039757</v>
+        <v>7039737</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1899,7 +1849,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1909,7 +1859,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>10:56</t>
+          <t>11:02</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Mkt riktigt i området</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1936,53 +1891,48 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>130826287</v>
+        <v>130826438</v>
       </c>
       <c r="B13" t="n">
-        <v>57884</v>
+        <v>79327</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Flinktorpet, Kälom, Offerdal, Jmt</t>
+          <t>Brännan, Brännan, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>461096</v>
+        <v>461220</v>
       </c>
       <c r="R13" t="n">
-        <v>7039690</v>
+        <v>7039590</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2011,7 +1961,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2021,12 +1971,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Barkfläkta klenare och grövre granar</t>
+          <t>Rikligt i området</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2053,27 +2003,27 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>130826478</v>
+        <v>130825823</v>
       </c>
       <c r="B14" t="n">
-        <v>57884</v>
+        <v>57950</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -2084,19 +2034,19 @@
       <c r="I14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Brännan, Kälom, Offerdal, Jmt</t>
+          <t>Flinktorpet, Kälom, Offerdal, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>461220</v>
+        <v>460947</v>
       </c>
       <c r="R14" t="n">
-        <v>7039590</v>
+        <v>7039711</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2128,7 +2078,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2138,12 +2088,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Födosök barkfläkt</t>
+          <t>Födosökshål på äldre döende gran.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2170,45 +2120,50 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>130826795</v>
+        <v>130826548</v>
       </c>
       <c r="B15" t="n">
-        <v>91809</v>
+        <v>56766</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1202</v>
+        <v>100077</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Utter</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lutra lutra</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Brännan, Brännan, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>461233</v>
+        <v>461350</v>
       </c>
       <c r="R15" t="n">
-        <v>7039441</v>
+        <v>7039491</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2240,7 +2195,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2250,7 +2205,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>11:29</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Kommit från väster och gått längs bäcken.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2277,10 +2237,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>130825822</v>
+        <v>130825533</v>
       </c>
       <c r="B16" t="n">
-        <v>89194</v>
+        <v>57953</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2288,34 +2248,39 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>510</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Flinktorpet, Flinktorpet, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>460947</v>
+        <v>460944</v>
       </c>
       <c r="R16" t="n">
-        <v>7039711</v>
+        <v>7039740</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2347,7 +2312,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>10:26</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2357,12 +2322,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>10:26</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>På granlåga</t>
+          <t>Färska spår födosök, barkfläkta klenare granar.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2389,10 +2354,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>130826291</v>
+        <v>130825852</v>
       </c>
       <c r="B17" t="n">
-        <v>91809</v>
+        <v>57953</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2400,37 +2365,42 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Flinktorpet, Flinktorpet, Jmt</t>
+          <t>Flinktorpet, Kälom, Offerdal, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>461106</v>
+        <v>460952</v>
       </c>
       <c r="R17" t="n">
-        <v>7039672</v>
+        <v>7039723</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2459,7 +2429,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2469,7 +2439,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>10:42</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Barkfläkta grövre och klenare granar.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2496,10 +2471,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>130826442</v>
+        <v>130826038</v>
       </c>
       <c r="B18" t="n">
-        <v>91809</v>
+        <v>57953</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2507,34 +2482,39 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Brännan, Brännan, Jmt</t>
+          <t>Flinktorpet, Kälom, Offerdal, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>461220</v>
+        <v>460969</v>
       </c>
       <c r="R18" t="n">
-        <v>7039590</v>
+        <v>7039684</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2566,7 +2546,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2576,7 +2556,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>10:51</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2603,10 +2588,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>130826276</v>
+        <v>130826274</v>
       </c>
       <c r="B19" t="n">
-        <v>79244</v>
+        <v>57953</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2614,27 +2599,32 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Flinktorpet, Flinktorpet, Jmt</t>
+          <t>Flinktorpet, Kälom, Offerdal, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
@@ -2644,7 +2634,7 @@
         <v>7039737</v>
       </c>
       <c r="S19" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2673,7 +2663,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2683,12 +2673,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>Mkt riktigt i området</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2715,10 +2705,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>130825533</v>
+        <v>130826287</v>
       </c>
       <c r="B20" t="n">
-        <v>57884</v>
+        <v>57953</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2751,14 +2741,14 @@
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Flinktorpet, Flinktorpet, Jmt</t>
+          <t>Flinktorpet, Kälom, Offerdal, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>460944</v>
+        <v>461096</v>
       </c>
       <c r="R20" t="n">
-        <v>7039740</v>
+        <v>7039690</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2790,7 +2780,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>10:26</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2800,12 +2790,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>10:26</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>Färska spår födosök, barkfläkta klenare granar.</t>
+          <t>Barkfläkta klenare och grövre granar</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2832,10 +2822,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>130826274</v>
+        <v>130826404</v>
       </c>
       <c r="B21" t="n">
-        <v>57884</v>
+        <v>57953</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2868,14 +2858,14 @@
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Flinktorpet, Kälom, Offerdal, Jmt</t>
+          <t>Brännan, Brännan, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>461045</v>
+        <v>461144</v>
       </c>
       <c r="R21" t="n">
-        <v>7039737</v>
+        <v>7039619</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2907,7 +2897,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2917,12 +2907,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Födosök barkfläkt</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2949,10 +2939,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>130826438</v>
+        <v>130826478</v>
       </c>
       <c r="B22" t="n">
-        <v>79244</v>
+        <v>57953</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2960,27 +2950,32 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Brännan, Brännan, Jmt</t>
+          <t>Brännan, Kälom, Offerdal, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
@@ -2990,7 +2985,7 @@
         <v>7039590</v>
       </c>
       <c r="S22" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3019,7 +3014,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3029,12 +3024,12 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Rikligt i området</t>
+          <t>Födosök barkfläkt</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3061,45 +3056,50 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>130826355</v>
+        <v>130826784</v>
       </c>
       <c r="B23" t="n">
-        <v>92536</v>
+        <v>57953</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>67</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Sprickporing</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Diplomitoporus crustulinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Bres.) Domański</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Flinktorpet, Flinktorpet, Jmt</t>
+          <t>Brännan, Kälom, Offerdal, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>461117</v>
+        <v>461233</v>
       </c>
       <c r="R23" t="n">
-        <v>7039629</v>
+        <v>7039438</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3131,7 +3131,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3141,12 +3141,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>11:10</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>På undersidan av lutande död gran.</t>
+          <t>Födosök barkfläk</t>
         </is>
       </c>
       <c r="AD23" t="b">

--- a/artfynd/A 933-2026 artfynd.xlsx
+++ b/artfynd/A 933-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY23"/>
+  <dimension ref="A1:AZ23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -784,6 +789,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130826355</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -896,6 +906,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130825822</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1003,6 +1018,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130826010</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1110,6 +1130,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130826137</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1217,6 +1242,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130826291</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1324,6 +1354,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130826442</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1431,6 +1466,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130826795</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1543,6 +1583,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130826011</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1664,6 +1709,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130825491</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1776,6 +1826,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130825838</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1888,6 +1943,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130826276</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2000,6 +2060,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130826438</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2117,6 +2182,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130825823</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2234,6 +2304,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130826548</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2351,6 +2426,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130825533</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2468,6 +2548,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130825852</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2585,6 +2670,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130826038</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2702,6 +2792,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130826274</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2819,6 +2914,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130826287</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2936,6 +3036,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130826404</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3053,6 +3158,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130826478</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3170,8 +3280,37 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130826784</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>